--- a/data/trans_camb/MCS12_SP_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 22,66</t>
+          <t>6,04; 23,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 23,83</t>
+          <t>6,41; 23,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 2,34</t>
+          <t>-15,62; 1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 31,0</t>
+          <t>14,0; 30,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 23,25</t>
+          <t>6,38; 23,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,62; -8,42</t>
+          <t>-25,55; -8,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 24,76</t>
+          <t>12,99; 24,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 21,0</t>
+          <t>8,94; 20,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -5,89</t>
+          <t>-17,41; -5,55</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 63,23</t>
+          <t>13,39; 64,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,23; 66,34</t>
+          <t>13,94; 64,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 5,52</t>
+          <t>-34,44; 3,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,16; 65,78</t>
+          <t>24,65; 65,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 49,85</t>
+          <t>10,81; 48,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,23; -17,48</t>
+          <t>-44,3; -18,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,25; 57,13</t>
+          <t>25,93; 57,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 47,31</t>
+          <t>18,38; 48,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,07; -13,84</t>
+          <t>-35,11; -12,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,11; -24,34</t>
+          <t>-37,08; -24,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-40,06; -28,79</t>
+          <t>-40,68; -28,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-34,05; -21,32</t>
+          <t>-35,17; -20,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,31; -20,39</t>
+          <t>-32,63; -20,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -33,82</t>
+          <t>-44,88; -33,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,06; -24,96</t>
+          <t>-36,24; -25,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,98; -24,43</t>
+          <t>-32,79; -24,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,05; -32,79</t>
+          <t>-41,15; -33,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-34,03; -24,71</t>
+          <t>-33,69; -24,86</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,03; -46,14</t>
+          <t>-62,99; -45,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,72; -53,8</t>
+          <t>-68,72; -53,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,84; -40,23</t>
+          <t>-60,19; -39,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,07; -30,92</t>
+          <t>-46,29; -31,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,0; -50,99</t>
+          <t>-63,47; -50,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,4; -37,84</t>
+          <t>-51,15; -38,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,76; -40,56</t>
+          <t>-51,42; -39,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,22; -54,12</t>
+          <t>-64,53; -54,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,1; -41,12</t>
+          <t>-52,98; -41,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 30,26</t>
+          <t>14,02; 28,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 29,66</t>
+          <t>14,55; 29,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 7,4</t>
+          <t>-6,57; 7,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,49; 32,6</t>
+          <t>17,59; 32,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,7; 28,02</t>
+          <t>12,03; 26,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 3,51</t>
+          <t>-10,48; 3,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,61; 29,06</t>
+          <t>18,2; 28,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,89; 26,16</t>
+          <t>15,64; 25,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,13</t>
+          <t>-6,9; 3,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,22; 133,02</t>
+          <t>45,56; 125,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,46; 127,88</t>
+          <t>46,5; 124,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 33,57</t>
+          <t>-22,42; 32,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,62; 89,78</t>
+          <t>38,64; 88,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,98; 76,6</t>
+          <t>27,89; 73,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 9,61</t>
+          <t>-23,13; 8,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,54; 94,27</t>
+          <t>48,73; 92,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,63; 82,38</t>
+          <t>42,53; 84,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 10,2</t>
+          <t>-18,71; 10,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 29,68</t>
+          <t>15,07; 29,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 9,78</t>
+          <t>-5,64; 9,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -1,24</t>
+          <t>-17,5; -0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,53; 30,98</t>
+          <t>18,07; 31,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 10,95</t>
+          <t>-3,71; 11,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 16,44</t>
+          <t>-16,45; 17,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,08; 28,93</t>
+          <t>19,04; 28,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,52</t>
+          <t>-2,09; 8,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 13,19</t>
+          <t>-12,41; 11,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,98; 78,5</t>
+          <t>33,28; 78,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 25,54</t>
+          <t>-12,18; 24,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,45; -3,19</t>
+          <t>-39,13; -0,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,31; 68,51</t>
+          <t>33,57; 67,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 23,36</t>
+          <t>-6,87; 25,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 34,11</t>
+          <t>-32,05; 38,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,76; 66,93</t>
+          <t>38,74; 66,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 19,84</t>
+          <t>-4,57; 19,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 29,68</t>
+          <t>-26,18; 26,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,43; -1,25</t>
+          <t>-21,5; -1,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,89; 46,59</t>
+          <t>30,24; 46,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,99; 36,66</t>
+          <t>18,84; 37,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 0,6</t>
+          <t>-19,13; 0,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,55; 36,7</t>
+          <t>20,12; 36,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,09; 30,7</t>
+          <t>16,49; 31,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -3,37</t>
+          <t>-18,04; -4,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,13; 39,11</t>
+          <t>27,8; 39,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,66; 33,2</t>
+          <t>19,2; 31,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -3,27</t>
+          <t>-40,45; -4,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55,4; 113,06</t>
+          <t>56,53; 112,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32,97; 87,56</t>
+          <t>36,4; 88,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 0,68</t>
+          <t>-29,05; 0,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,01; 69,82</t>
+          <t>30,85; 67,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,08; 57,18</t>
+          <t>24,53; 57,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -6,69</t>
+          <t>-31,19; -8,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>46,42; 78,48</t>
+          <t>47,02; 78,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,2; 67,75</t>
+          <t>32,38; 64,03</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>11,26; 29,06</t>
+          <t>12,3; 28,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 8,48</t>
+          <t>-6,94; 9,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 8,13</t>
+          <t>-7,12; 7,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8,46; 24,83</t>
+          <t>8,37; 25,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 7,22</t>
+          <t>-9,32; 7,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -1,13</t>
+          <t>-16,21; -0,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,83; 23,89</t>
+          <t>13,04; 24,65</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 5,97</t>
+          <t>-5,38; 5,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 0,58</t>
+          <t>-9,96; 0,73</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29,15; 98,24</t>
+          <t>32,61; 96,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 27,5</t>
+          <t>-19,32; 30,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 27,16</t>
+          <t>-18,83; 26,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15,87; 59,09</t>
+          <t>16,39; 60,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 17,3</t>
+          <t>-18,79; 17,93</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,33; -1,91</t>
+          <t>-32,05; -1,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,34; 64,59</t>
+          <t>29,36; 65,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 15,62</t>
+          <t>-12,4; 14,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 1,69</t>
+          <t>-22,86; 2,12</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>14,16; 25,07</t>
+          <t>14,53; 25,7</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11,51; 22,59</t>
+          <t>11,82; 23,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10,4; 23,39</t>
+          <t>11,22; 23,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11,16; 22,0</t>
+          <t>10,93; 21,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,8; 14,24</t>
+          <t>3,15; 13,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,75; 42,09</t>
+          <t>12,48; 38,98</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,58; 22,17</t>
+          <t>14,61; 22,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,14; 16,89</t>
+          <t>9,08; 17,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,34; 37,04</t>
+          <t>14,36; 36,8</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>38,35; 78,47</t>
+          <t>38,41; 80,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30,87; 70,01</t>
+          <t>30,95; 71,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26,95; 73,16</t>
+          <t>29,54; 71,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,78; 48,43</t>
+          <t>21,27; 46,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,41; 30,92</t>
+          <t>5,44; 29,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,53; 94,49</t>
+          <t>24,98; 81,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,31; 55,16</t>
+          <t>32,82; 57,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,88; 42,32</t>
+          <t>20,39; 42,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,4; 91,29</t>
+          <t>33,53; 91,02</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 3,84</t>
+          <t>-7,04; 3,65</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 7,24</t>
+          <t>-3,3; 7,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 0,72</t>
+          <t>-36,28; 0,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 8,79</t>
+          <t>-1,79; 8,5</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,15</t>
+          <t>-6,65; 3,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,19</t>
+          <t>-3,28; 6,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,66</t>
+          <t>-3,0; 4,42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,65</t>
+          <t>-3,42; 4,01</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 1,16</t>
+          <t>-29,13; 0,91</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 7,72</t>
+          <t>-13,09; 7,35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 14,55</t>
+          <t>-6,08; 14,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 1,25</t>
+          <t>-68,74; 0,83</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 16,01</t>
+          <t>-2,93; 15,29</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 5,52</t>
+          <t>-10,96; 6,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 11,29</t>
+          <t>-5,36; 11,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 8,72</t>
+          <t>-5,23; 8,19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 6,65</t>
+          <t>-5,97; 7,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 1,95</t>
+          <t>-51,56; 1,59</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,15</t>
+          <t>3,34; 8,3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,57</t>
+          <t>2,39; 7,51</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -0,96</t>
+          <t>-13,71; -0,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,96</t>
+          <t>5,38; 9,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,95</t>
+          <t>-1,74; 3,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 8,24</t>
+          <t>-4,2; 7,91</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,56</t>
+          <t>5,19; 8,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,73</t>
+          <t>1,06; 4,52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,0</t>
+          <t>-7,29; 2,58</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,29; 19,58</t>
+          <t>7,57; 19,9</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5,75; 17,82</t>
+          <t>5,38; 17,95</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-33,67; -2,26</t>
+          <t>-31,02; -1,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9,41; 18,95</t>
+          <t>9,56; 18,62</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,59</t>
+          <t>-3,09; 6,15</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 15,27</t>
+          <t>-7,69; 14,62</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10,18; 17,89</t>
+          <t>10,41; 18,21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,93</t>
+          <t>2,11; 9,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 4,23</t>
+          <t>-14,96; 5,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,46</t>
+          <t>-7,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,8</t>
+          <t>-17,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,04</t>
+          <t>-12,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 23,74</t>
+          <t>6,5; 23,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 23,9</t>
+          <t>5,87; 22,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 1,31</t>
+          <t>-15,07; 0,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 30,42</t>
+          <t>13,86; 30,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 23,2</t>
+          <t>5,54; 22,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,55; -8,85</t>
+          <t>-25,15; -9,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 24,66</t>
+          <t>12,52; 24,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 20,79</t>
+          <t>8,78; 21,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -5,55</t>
+          <t>-17,49; -6,48</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-18,13%</t>
+          <t>-18,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,11%</t>
+          <t>-32,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-25,82%</t>
+          <t>-26,15%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 64,52</t>
+          <t>14,08; 64,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,94; 64,64</t>
+          <t>12,46; 61,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 3,58</t>
+          <t>-33,34; 0,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,65; 65,13</t>
+          <t>25,08; 66,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 48,4</t>
+          <t>9,41; 47,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,3; -18,5</t>
+          <t>-43,69; -19,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,93; 57,06</t>
+          <t>25,17; 57,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 48,72</t>
+          <t>16,94; 48,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,11; -12,58</t>
+          <t>-35,41; -14,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-28,17</t>
+          <t>-28,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-30,5</t>
+          <t>-30,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-29,42</t>
+          <t>-29,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-37,08; -24,12</t>
+          <t>-36,78; -24,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -28,45</t>
+          <t>-40,3; -27,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -20,83</t>
+          <t>-34,35; -21,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,63; -20,5</t>
+          <t>-33,22; -20,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,88; -33,39</t>
+          <t>-45,03; -33,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,24; -25,19</t>
+          <t>-36,27; -25,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,79; -24,13</t>
+          <t>-32,86; -23,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,15; -33,24</t>
+          <t>-40,73; -32,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-33,69; -24,86</t>
+          <t>-33,83; -25,04</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-50,51%</t>
+          <t>-50,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-44,65%</t>
+          <t>-45,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-47,37%</t>
+          <t>-47,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,99; -45,77</t>
+          <t>-62,7; -46,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,72; -53,6</t>
+          <t>-68,59; -53,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,19; -39,26</t>
+          <t>-59,07; -39,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,29; -31,38</t>
+          <t>-47,48; -31,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,47; -50,05</t>
+          <t>-63,78; -51,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,15; -38,53</t>
+          <t>-50,73; -38,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,42; -39,88</t>
+          <t>-51,3; -39,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,53; -54,98</t>
+          <t>-63,98; -54,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,98; -41,38</t>
+          <t>-53,1; -41,57</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-3,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 28,95</t>
+          <t>14,52; 29,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 29,61</t>
+          <t>15,04; 29,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 7,16</t>
+          <t>-5,8; 7,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 32,67</t>
+          <t>17,25; 33,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 26,99</t>
+          <t>12,73; 27,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 3,15</t>
+          <t>-10,72; 3,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,2; 28,94</t>
+          <t>18,26; 29,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,95</t>
+          <t>15,34; 26,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,21</t>
+          <t>-6,01; 3,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,51%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,19%</t>
+          <t>-7,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,29%</t>
+          <t>-2,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45,56; 125,76</t>
+          <t>47,82; 125,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,5; 124,63</t>
+          <t>49,82; 128,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 32,22</t>
+          <t>-19,31; 32,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,64; 88,62</t>
+          <t>38,07; 90,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,89; 73,72</t>
+          <t>28,78; 76,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 8,61</t>
+          <t>-23,65; 8,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,73; 92,05</t>
+          <t>49,41; 92,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,53; 84,09</t>
+          <t>41,51; 84,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 10,37</t>
+          <t>-16,22; 10,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,56</t>
+          <t>-10,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-9,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-9,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,07; 29,76</t>
+          <t>15,38; 30,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 9,57</t>
+          <t>-4,83; 9,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -0,65</t>
+          <t>-18,84; -2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,07; 31,22</t>
+          <t>17,65; 30,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 11,51</t>
+          <t>-3,79; 10,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 17,45</t>
+          <t>-15,94; -2,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,49</t>
+          <t>18,44; 28,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 8,52</t>
+          <t>-2,25; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 11,92</t>
+          <t>-14,31; -4,14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-22,93%</t>
+          <t>-24,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,39%</t>
+          <t>-17,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,91%</t>
+          <t>-20,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,28; 78,75</t>
+          <t>34,01; 79,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 24,98</t>
+          <t>-10,67; 25,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,13; -0,83</t>
+          <t>-41,25; -5,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,57; 67,62</t>
+          <t>32,37; 66,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 25,14</t>
+          <t>-6,94; 21,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 38,33</t>
+          <t>-29,43; -4,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,74; 66,06</t>
+          <t>37,92; 65,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 19,09</t>
+          <t>-4,59; 19,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 26,92</t>
+          <t>-29,63; -9,26</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28,35</t>
+          <t>26,94</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>23,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26,23</t>
+          <t>25,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,5; -1,93</t>
+          <t>-20,62; -1,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30,24; 46,8</t>
+          <t>31,45; 47,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,84; 37,46</t>
+          <t>17,75; 36,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 0,53</t>
+          <t>-19,07; -0,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,12; 36,38</t>
+          <t>19,98; 36,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,49; 31,49</t>
+          <t>15,14; 30,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,04; -4,2</t>
+          <t>-16,9; -2,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27,8; 39,0</t>
+          <t>27,36; 39,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,2; 31,95</t>
+          <t>19,39; 31,14</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,45; -4,59</t>
+          <t>-39,65; -4,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>56,53; 112,04</t>
+          <t>58,92; 115,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36,4; 88,09</t>
+          <t>34,73; 89,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 0,99</t>
+          <t>-29,55; -0,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,85; 67,67</t>
+          <t>31,12; 70,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,53; 57,88</t>
+          <t>22,59; 55,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,19; -8,19</t>
+          <t>-29,73; -4,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>47,02; 78,31</t>
+          <t>47,35; 80,33</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>32,38; 64,03</t>
+          <t>33,46; 62,82</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-8,91</t>
+          <t>-8,85</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-4,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>12,3; 28,81</t>
+          <t>11,92; 28,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 9,05</t>
+          <t>-8,03; 8,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 7,93</t>
+          <t>-7,6; 7,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8,37; 25,43</t>
+          <t>8,28; 24,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 7,56</t>
+          <t>-9,39; 7,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,21; -0,36</t>
+          <t>-16,53; -1,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,04; 24,65</t>
+          <t>12,63; 24,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 5,59</t>
+          <t>-6,46; 5,67</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 0,73</t>
+          <t>-9,87; 1,24</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-19,14%</t>
+          <t>-19,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-11,12%</t>
+          <t>-11,02%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32,61; 96,97</t>
+          <t>30,42; 94,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 30,32</t>
+          <t>-20,77; 28,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 26,54</t>
+          <t>-20,3; 24,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16,39; 60,96</t>
+          <t>16,07; 58,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 17,93</t>
+          <t>-18,61; 17,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,05; -1,07</t>
+          <t>-32,18; -2,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,36; 65,43</t>
+          <t>28,48; 67,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 14,91</t>
+          <t>-14,76; 15,43</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 2,12</t>
+          <t>-22,56; 3,42</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>16,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,66</t>
+          <t>15,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>14,53; 25,7</t>
+          <t>13,9; 25,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11,82; 23,21</t>
+          <t>11,72; 23,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,22; 23,32</t>
+          <t>10,23; 22,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10,93; 21,71</t>
+          <t>11,22; 22,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,9</t>
+          <t>3,18; 14,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,48; 38,98</t>
+          <t>8,59; 19,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,61; 22,81</t>
+          <t>13,9; 21,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,08; 17,05</t>
+          <t>9,16; 16,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,36; 36,8</t>
+          <t>11,42; 19,17</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>38,41; 80,42</t>
+          <t>36,67; 78,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30,95; 71,48</t>
+          <t>30,65; 71,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29,54; 71,26</t>
+          <t>26,7; 70,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,27; 46,62</t>
+          <t>21,27; 49,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,44; 29,27</t>
+          <t>6,17; 31,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,98; 81,87</t>
+          <t>16,5; 42,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,82; 57,13</t>
+          <t>31,47; 54,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,39; 42,28</t>
+          <t>20,78; 42,4</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,53; 91,02</t>
+          <t>25,65; 47,57</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-14,49</t>
+          <t>-1,78</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-8,14</t>
+          <t>-0,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 3,65</t>
+          <t>-6,52; 4,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,26</t>
+          <t>-2,69; 7,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 0,44</t>
+          <t>-7,27; 3,71</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 8,5</t>
+          <t>-1,45; 8,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 3,36</t>
+          <t>-6,74; 3,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 6,14</t>
+          <t>-4,18; 5,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,42</t>
+          <t>-2,5; 4,75</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,01</t>
+          <t>-3,13; 4,3</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 0,91</t>
+          <t>-3,85; 3,19</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-27,87%</t>
+          <t>-3,43%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-14,69%</t>
+          <t>-0,87%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 7,35</t>
+          <t>-12,0; 8,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 14,42</t>
+          <t>-5,06; 15,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,74; 0,83</t>
+          <t>-13,18; 7,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 15,29</t>
+          <t>-2,39; 15,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 6,01</t>
+          <t>-11,0; 5,77</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 11,0</t>
+          <t>-6,99; 10,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 8,19</t>
+          <t>-4,46; 8,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 7,43</t>
+          <t>-5,47; 8,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 1,59</t>
+          <t>-6,73; 6,04</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,3</t>
+          <t>3,3; 8,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,51</t>
+          <t>2,48; 7,36</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,66</t>
+          <t>-3,87; 1,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,88</t>
+          <t>5,52; 10,23</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,26</t>
+          <t>-1,98; 2,89</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,91</t>
+          <t>-5,84; -1,08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,68</t>
+          <t>4,82; 8,34</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,52</t>
+          <t>0,94; 4,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,58</t>
+          <t>-4,17; -0,77</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-10,6%</t>
+          <t>-3,18%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>-6,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-4,82%</t>
+          <t>-4,83%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,9</t>
+          <t>7,34; 19,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5,38; 17,95</t>
+          <t>5,5; 17,51</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -1,58</t>
+          <t>-8,77; 2,78</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9,56; 18,62</t>
+          <t>9,96; 19,25</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,15</t>
+          <t>-3,57; 5,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 14,62</t>
+          <t>-10,48; -2,0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,21</t>
+          <t>9,69; 17,42</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,39</t>
+          <t>1,87; 9,22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 5,36</t>
+          <t>-8,37; -1,58</t>
         </is>
       </c>
     </row>
